--- a/Analysis/tables/B4_correlation_matrix.xlsx
+++ b/Analysis/tables/B4_correlation_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,26 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>team_early_cs_10</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_early_gold_adv</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_early_takedowns</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>avg_skill_index</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>win</t>
         </is>
       </c>
@@ -510,6 +530,18 @@
         <v>-0.3420024878072749</v>
       </c>
       <c r="L2" t="n">
+        <v>-0.1562225515009772</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.111576100271809</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.2906152409289892</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.1583651654439985</v>
+      </c>
+      <c r="P2" t="n">
         <v>-0.3576667087181305</v>
       </c>
     </row>
@@ -550,6 +582,18 @@
         <v>0.3676106482907877</v>
       </c>
       <c r="L3" t="n">
+        <v>0.170794186269888</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1158043341689623</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2506004896630763</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1603247848424918</v>
+      </c>
+      <c r="P3" t="n">
         <v>0.4453962541332376</v>
       </c>
     </row>
@@ -590,6 +634,18 @@
         <v>0.1929209503503234</v>
       </c>
       <c r="L4" t="n">
+        <v>0.1021256343192618</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07102085315712181</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1862892212239877</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.08866482534047573</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.1183351521260377</v>
       </c>
     </row>
@@ -630,6 +686,18 @@
         <v>-0.1290240059758537</v>
       </c>
       <c r="L5" t="n">
+        <v>0.2034052230001303</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2378333044626195</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4194935335138384</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.07914248975183934</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.6414819591769791</v>
       </c>
     </row>
@@ -670,6 +738,18 @@
         <v>-0.2135623468217421</v>
       </c>
       <c r="L6" t="n">
+        <v>0.6602849572318474</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1599221976235699</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02373394647441179</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1388146056626134</v>
+      </c>
+      <c r="P6" t="n">
         <v>0.3897642475055056</v>
       </c>
     </row>
@@ -710,6 +790,18 @@
         <v>0.9297320978946807</v>
       </c>
       <c r="L7" t="n">
+        <v>0.1215811508461761</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04235821947137054</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1442218818085809</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4296089595390347</v>
+      </c>
+      <c r="P7" t="n">
         <v>0.2786731471618311</v>
       </c>
     </row>
@@ -750,6 +842,18 @@
         <v>0.8812379841841576</v>
       </c>
       <c r="L8" t="n">
+        <v>0.06283999941047752</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03540066336569297</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1596100697147768</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4310611659537686</v>
+      </c>
+      <c r="P8" t="n">
         <v>0.2079570746320229</v>
       </c>
     </row>
@@ -790,6 +894,18 @@
         <v>0.8570764211685993</v>
       </c>
       <c r="L9" t="n">
+        <v>0.1678587955279427</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.01198078210656666</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.01396067235011323</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4045763290076704</v>
+      </c>
+      <c r="P9" t="n">
         <v>0.09441862551326773</v>
       </c>
     </row>
@@ -830,6 +946,18 @@
         <v>-1.87295510828316e-05</v>
       </c>
       <c r="L10" t="n">
+        <v>0.1140119229462849</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.181648487436634</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1765675690884783</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.003422704843132643</v>
+      </c>
+      <c r="P10" t="n">
         <v>0.137704944053695</v>
       </c>
     </row>
@@ -870,46 +998,278 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
+        <v>0.02420036144205708</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.05447468995109983</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.05262853034406193</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4564264245854779</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.595845689296493e-16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>team_early_cs_10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.1562225515009772</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.170794186269888</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1021256343192618</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2034052230001303</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6602849572318474</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1215811508461761</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.06283999941047752</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1678587955279427</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1140119229462849</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.02420036144205708</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.170557585250863</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.06331712665080808</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02201341668103764</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2097905885300987</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>team_early_gold_adv</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.111576100271809</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1158043341689623</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.07102085315712181</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2378333044626195</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1599221976235699</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04235821947137054</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.03540066336569297</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.01198078210656666</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.181648487436634</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.05447468995109983</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.170557585250863</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2720608942110319</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.03023328850400138</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2128445093931978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>team_early_takedowns</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2906152409289892</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2506004896630763</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1862892212239877</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4194935335138384</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.02373394647441179</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1442218818085809</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1596100697147768</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01396067235011323</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1765675690884783</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.05262853034406193</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.06331712665080808</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2720608942110319</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003020718970017998</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3372544863173761</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>avg_skill_index</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.1583651654439985</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1603247848424918</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.08866482534047573</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.07914248975183934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1388146056626134</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4296089595390347</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4310611659537686</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4045763290076704</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.003422704843132643</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.4564264245854779</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.02201341668103764</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.03023328850400138</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.003020718970017998</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.02820697928214157</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>win</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B16" t="n">
         <v>-0.3576667087181305</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C16" t="n">
         <v>0.4453962541332376</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D16" t="n">
         <v>0.1183351521260377</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E16" t="n">
         <v>0.6414819591769791</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F16" t="n">
         <v>0.3897642475055056</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G16" t="n">
         <v>0.2786731471618311</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H16" t="n">
         <v>0.2079570746320229</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I16" t="n">
         <v>0.09441862551326773</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J16" t="n">
         <v>0.137704944053695</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K16" t="n">
         <v>1.595845689296493e-16</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L16" t="n">
+        <v>0.2097905885300987</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2128445093931978</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3372544863173761</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.02820697928214157</v>
+      </c>
+      <c r="P16" t="n">
         <v>1</v>
       </c>
     </row>
